--- a/Data/Final Data/No Controls/State/STATE_NO_CONTROLS_VIC_QLD_New_Bonds.xlsx
+++ b/Data/Final Data/No Controls/State/STATE_NO_CONTROLS_VIC_QLD_New_Bonds.xlsx
@@ -361,7 +361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -409,6 +409,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Running_Quarter</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -441,6 +446,9 @@
       <c r="H2" s="2">
         <v>43190</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -473,6 +481,9 @@
       <c r="H3" s="2">
         <v>43281</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -505,6 +516,9 @@
       <c r="H4" s="2">
         <v>43373</v>
       </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -537,6 +551,9 @@
       <c r="H5" s="2">
         <v>43465</v>
       </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -569,6 +586,9 @@
       <c r="H6" s="2">
         <v>43555</v>
       </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -601,6 +621,9 @@
       <c r="H7" s="2">
         <v>43646</v>
       </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -633,6 +656,9 @@
       <c r="H8" s="2">
         <v>43738</v>
       </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -665,6 +691,9 @@
       <c r="H9" s="2">
         <v>43830</v>
       </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -697,6 +726,9 @@
       <c r="H10" s="2">
         <v>43921</v>
       </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -729,6 +761,9 @@
       <c r="H11" s="2">
         <v>44012</v>
       </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -761,6 +796,9 @@
       <c r="H12" s="2">
         <v>44104</v>
       </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -793,6 +831,9 @@
       <c r="H13" s="2">
         <v>44196</v>
       </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -825,6 +866,9 @@
       <c r="H14" s="2">
         <v>44286</v>
       </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -857,6 +901,9 @@
       <c r="H15" s="2">
         <v>44377</v>
       </c>
+      <c r="I15">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -889,6 +936,9 @@
       <c r="H16" s="2">
         <v>44469</v>
       </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -921,6 +971,9 @@
       <c r="H17" s="2">
         <v>44561</v>
       </c>
+      <c r="I17">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -953,6 +1006,9 @@
       <c r="H18" s="2">
         <v>44651</v>
       </c>
+      <c r="I18">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -985,6 +1041,9 @@
       <c r="H19" s="2">
         <v>44742</v>
       </c>
+      <c r="I19">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1017,6 +1076,9 @@
       <c r="H20" s="2">
         <v>44834</v>
       </c>
+      <c r="I20">
+        <v>19</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1049,6 +1111,9 @@
       <c r="H21" s="2">
         <v>44926</v>
       </c>
+      <c r="I21">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1081,6 +1146,9 @@
       <c r="H22" s="2">
         <v>43190</v>
       </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1113,6 +1181,9 @@
       <c r="H23" s="2">
         <v>43281</v>
       </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1145,6 +1216,9 @@
       <c r="H24" s="2">
         <v>43373</v>
       </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1177,6 +1251,9 @@
       <c r="H25" s="2">
         <v>43465</v>
       </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1209,6 +1286,9 @@
       <c r="H26" s="2">
         <v>43555</v>
       </c>
+      <c r="I26">
+        <v>5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1241,6 +1321,9 @@
       <c r="H27" s="2">
         <v>43646</v>
       </c>
+      <c r="I27">
+        <v>6</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1273,6 +1356,9 @@
       <c r="H28" s="2">
         <v>43738</v>
       </c>
+      <c r="I28">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1305,6 +1391,9 @@
       <c r="H29" s="2">
         <v>43830</v>
       </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1337,6 +1426,9 @@
       <c r="H30" s="2">
         <v>43921</v>
       </c>
+      <c r="I30">
+        <v>9</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1369,6 +1461,9 @@
       <c r="H31" s="2">
         <v>44012</v>
       </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1401,6 +1496,9 @@
       <c r="H32" s="2">
         <v>44104</v>
       </c>
+      <c r="I32">
+        <v>11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1433,6 +1531,9 @@
       <c r="H33" s="2">
         <v>44196</v>
       </c>
+      <c r="I33">
+        <v>12</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1465,6 +1566,9 @@
       <c r="H34" s="2">
         <v>44286</v>
       </c>
+      <c r="I34">
+        <v>13</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1497,6 +1601,9 @@
       <c r="H35" s="2">
         <v>44377</v>
       </c>
+      <c r="I35">
+        <v>14</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1529,6 +1636,9 @@
       <c r="H36" s="2">
         <v>44469</v>
       </c>
+      <c r="I36">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1561,6 +1671,9 @@
       <c r="H37" s="2">
         <v>44561</v>
       </c>
+      <c r="I37">
+        <v>16</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1593,6 +1706,9 @@
       <c r="H38" s="2">
         <v>44651</v>
       </c>
+      <c r="I38">
+        <v>17</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1625,6 +1741,9 @@
       <c r="H39" s="2">
         <v>44742</v>
       </c>
+      <c r="I39">
+        <v>18</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1657,6 +1776,9 @@
       <c r="H40" s="2">
         <v>44834</v>
       </c>
+      <c r="I40">
+        <v>19</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1688,6 +1810,9 @@
       </c>
       <c r="H41" s="2">
         <v>44926</v>
+      </c>
+      <c r="I41">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1697,7 +1822,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -1745,6 +1870,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Running_Quarter</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1777,6 +1907,9 @@
       <c r="H2" s="2">
         <v>43190</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1809,6 +1942,9 @@
       <c r="H3" s="2">
         <v>43281</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1841,6 +1977,9 @@
       <c r="H4" s="2">
         <v>43373</v>
       </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1873,6 +2012,9 @@
       <c r="H5" s="2">
         <v>43465</v>
       </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1905,6 +2047,9 @@
       <c r="H6" s="2">
         <v>43555</v>
       </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1937,6 +2082,9 @@
       <c r="H7" s="2">
         <v>43646</v>
       </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1969,6 +2117,9 @@
       <c r="H8" s="2">
         <v>43738</v>
       </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2001,6 +2152,9 @@
       <c r="H9" s="2">
         <v>43830</v>
       </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2033,6 +2187,9 @@
       <c r="H10" s="2">
         <v>43921</v>
       </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2065,6 +2222,9 @@
       <c r="H11" s="2">
         <v>44012</v>
       </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2097,6 +2257,9 @@
       <c r="H12" s="2">
         <v>44104</v>
       </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2129,6 +2292,9 @@
       <c r="H13" s="2">
         <v>44196</v>
       </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2161,6 +2327,9 @@
       <c r="H14" s="2">
         <v>44286</v>
       </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2193,6 +2362,9 @@
       <c r="H15" s="2">
         <v>44377</v>
       </c>
+      <c r="I15">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2225,6 +2397,9 @@
       <c r="H16" s="2">
         <v>44469</v>
       </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2257,6 +2432,9 @@
       <c r="H17" s="2">
         <v>44561</v>
       </c>
+      <c r="I17">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2289,6 +2467,9 @@
       <c r="H18" s="2">
         <v>44651</v>
       </c>
+      <c r="I18">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2321,6 +2502,9 @@
       <c r="H19" s="2">
         <v>44742</v>
       </c>
+      <c r="I19">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2353,6 +2537,9 @@
       <c r="H20" s="2">
         <v>44834</v>
       </c>
+      <c r="I20">
+        <v>19</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2385,6 +2572,9 @@
       <c r="H21" s="2">
         <v>44926</v>
       </c>
+      <c r="I21">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2417,6 +2607,9 @@
       <c r="H22" s="2">
         <v>43190</v>
       </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2449,6 +2642,9 @@
       <c r="H23" s="2">
         <v>43281</v>
       </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2481,6 +2677,9 @@
       <c r="H24" s="2">
         <v>43373</v>
       </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2513,6 +2712,9 @@
       <c r="H25" s="2">
         <v>43465</v>
       </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2545,6 +2747,9 @@
       <c r="H26" s="2">
         <v>43555</v>
       </c>
+      <c r="I26">
+        <v>5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2782,9 @@
       <c r="H27" s="2">
         <v>43646</v>
       </c>
+      <c r="I27">
+        <v>6</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2609,6 +2817,9 @@
       <c r="H28" s="2">
         <v>43738</v>
       </c>
+      <c r="I28">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2641,6 +2852,9 @@
       <c r="H29" s="2">
         <v>43830</v>
       </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2673,6 +2887,9 @@
       <c r="H30" s="2">
         <v>43921</v>
       </c>
+      <c r="I30">
+        <v>9</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2705,6 +2922,9 @@
       <c r="H31" s="2">
         <v>44012</v>
       </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2737,6 +2957,9 @@
       <c r="H32" s="2">
         <v>44104</v>
       </c>
+      <c r="I32">
+        <v>11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2769,6 +2992,9 @@
       <c r="H33" s="2">
         <v>44196</v>
       </c>
+      <c r="I33">
+        <v>12</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2801,6 +3027,9 @@
       <c r="H34" s="2">
         <v>44286</v>
       </c>
+      <c r="I34">
+        <v>13</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2833,6 +3062,9 @@
       <c r="H35" s="2">
         <v>44377</v>
       </c>
+      <c r="I35">
+        <v>14</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2865,6 +3097,9 @@
       <c r="H36" s="2">
         <v>44469</v>
       </c>
+      <c r="I36">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2897,6 +3132,9 @@
       <c r="H37" s="2">
         <v>44561</v>
       </c>
+      <c r="I37">
+        <v>16</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2929,6 +3167,9 @@
       <c r="H38" s="2">
         <v>44651</v>
       </c>
+      <c r="I38">
+        <v>17</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2961,6 +3202,9 @@
       <c r="H39" s="2">
         <v>44742</v>
       </c>
+      <c r="I39">
+        <v>18</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2993,6 +3237,9 @@
       <c r="H40" s="2">
         <v>44834</v>
       </c>
+      <c r="I40">
+        <v>19</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3024,6 +3271,9 @@
       </c>
       <c r="H41" s="2">
         <v>44926</v>
+      </c>
+      <c r="I41">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3033,7 +3283,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -3081,6 +3331,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Running_Quarter</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3113,6 +3368,9 @@
       <c r="H2" s="2">
         <v>43190</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3145,6 +3403,9 @@
       <c r="H3" s="2">
         <v>43281</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3177,6 +3438,9 @@
       <c r="H4" s="2">
         <v>43373</v>
       </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3209,6 +3473,9 @@
       <c r="H5" s="2">
         <v>43465</v>
       </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3241,6 +3508,9 @@
       <c r="H6" s="2">
         <v>43555</v>
       </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3273,6 +3543,9 @@
       <c r="H7" s="2">
         <v>43646</v>
       </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3305,6 +3578,9 @@
       <c r="H8" s="2">
         <v>43738</v>
       </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3337,6 +3613,9 @@
       <c r="H9" s="2">
         <v>43830</v>
       </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3369,6 +3648,9 @@
       <c r="H10" s="2">
         <v>43921</v>
       </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3401,6 +3683,9 @@
       <c r="H11" s="2">
         <v>44012</v>
       </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3433,6 +3718,9 @@
       <c r="H12" s="2">
         <v>44104</v>
       </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3465,6 +3753,9 @@
       <c r="H13" s="2">
         <v>44196</v>
       </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3497,6 +3788,9 @@
       <c r="H14" s="2">
         <v>44286</v>
       </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3529,6 +3823,9 @@
       <c r="H15" s="2">
         <v>44377</v>
       </c>
+      <c r="I15">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3561,6 +3858,9 @@
       <c r="H16" s="2">
         <v>44469</v>
       </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3593,6 +3893,9 @@
       <c r="H17" s="2">
         <v>44561</v>
       </c>
+      <c r="I17">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3625,6 +3928,9 @@
       <c r="H18" s="2">
         <v>44651</v>
       </c>
+      <c r="I18">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3657,6 +3963,9 @@
       <c r="H19" s="2">
         <v>44742</v>
       </c>
+      <c r="I19">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3689,6 +3998,9 @@
       <c r="H20" s="2">
         <v>44834</v>
       </c>
+      <c r="I20">
+        <v>19</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3721,6 +4033,9 @@
       <c r="H21" s="2">
         <v>44926</v>
       </c>
+      <c r="I21">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3753,6 +4068,9 @@
       <c r="H22" s="2">
         <v>43190</v>
       </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3785,6 +4103,9 @@
       <c r="H23" s="2">
         <v>43281</v>
       </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3817,6 +4138,9 @@
       <c r="H24" s="2">
         <v>43373</v>
       </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3849,6 +4173,9 @@
       <c r="H25" s="2">
         <v>43465</v>
       </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3881,6 +4208,9 @@
       <c r="H26" s="2">
         <v>43555</v>
       </c>
+      <c r="I26">
+        <v>5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3913,6 +4243,9 @@
       <c r="H27" s="2">
         <v>43646</v>
       </c>
+      <c r="I27">
+        <v>6</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3945,6 +4278,9 @@
       <c r="H28" s="2">
         <v>43738</v>
       </c>
+      <c r="I28">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3977,6 +4313,9 @@
       <c r="H29" s="2">
         <v>43830</v>
       </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4009,6 +4348,9 @@
       <c r="H30" s="2">
         <v>43921</v>
       </c>
+      <c r="I30">
+        <v>9</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4041,6 +4383,9 @@
       <c r="H31" s="2">
         <v>44012</v>
       </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4073,6 +4418,9 @@
       <c r="H32" s="2">
         <v>44104</v>
       </c>
+      <c r="I32">
+        <v>11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4105,6 +4453,9 @@
       <c r="H33" s="2">
         <v>44196</v>
       </c>
+      <c r="I33">
+        <v>12</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4137,6 +4488,9 @@
       <c r="H34" s="2">
         <v>44286</v>
       </c>
+      <c r="I34">
+        <v>13</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4169,6 +4523,9 @@
       <c r="H35" s="2">
         <v>44377</v>
       </c>
+      <c r="I35">
+        <v>14</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4201,6 +4558,9 @@
       <c r="H36" s="2">
         <v>44469</v>
       </c>
+      <c r="I36">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4233,6 +4593,9 @@
       <c r="H37" s="2">
         <v>44561</v>
       </c>
+      <c r="I37">
+        <v>16</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4265,6 +4628,9 @@
       <c r="H38" s="2">
         <v>44651</v>
       </c>
+      <c r="I38">
+        <v>17</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4297,6 +4663,9 @@
       <c r="H39" s="2">
         <v>44742</v>
       </c>
+      <c r="I39">
+        <v>18</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4329,6 +4698,9 @@
       <c r="H40" s="2">
         <v>44834</v>
       </c>
+      <c r="I40">
+        <v>19</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4360,6 +4732,9 @@
       </c>
       <c r="H41" s="2">
         <v>44926</v>
+      </c>
+      <c r="I41">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4369,7 +4744,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -4417,6 +4792,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Running_Quarter</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4449,6 +4829,9 @@
       <c r="H2" s="2">
         <v>43190</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4481,6 +4864,9 @@
       <c r="H3" s="2">
         <v>43281</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4513,6 +4899,9 @@
       <c r="H4" s="2">
         <v>43373</v>
       </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4545,6 +4934,9 @@
       <c r="H5" s="2">
         <v>43465</v>
       </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4577,6 +4969,9 @@
       <c r="H6" s="2">
         <v>43555</v>
       </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4609,6 +5004,9 @@
       <c r="H7" s="2">
         <v>43646</v>
       </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4641,6 +5039,9 @@
       <c r="H8" s="2">
         <v>43738</v>
       </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4673,6 +5074,9 @@
       <c r="H9" s="2">
         <v>43830</v>
       </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4705,6 +5109,9 @@
       <c r="H10" s="2">
         <v>43921</v>
       </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4737,6 +5144,9 @@
       <c r="H11" s="2">
         <v>44012</v>
       </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4769,6 +5179,9 @@
       <c r="H12" s="2">
         <v>44104</v>
       </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4801,6 +5214,9 @@
       <c r="H13" s="2">
         <v>44196</v>
       </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4833,6 +5249,9 @@
       <c r="H14" s="2">
         <v>44286</v>
       </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4865,6 +5284,9 @@
       <c r="H15" s="2">
         <v>44377</v>
       </c>
+      <c r="I15">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4897,6 +5319,9 @@
       <c r="H16" s="2">
         <v>44469</v>
       </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4929,6 +5354,9 @@
       <c r="H17" s="2">
         <v>44561</v>
       </c>
+      <c r="I17">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4961,6 +5389,9 @@
       <c r="H18" s="2">
         <v>44651</v>
       </c>
+      <c r="I18">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4993,6 +5424,9 @@
       <c r="H19" s="2">
         <v>44742</v>
       </c>
+      <c r="I19">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5025,6 +5459,9 @@
       <c r="H20" s="2">
         <v>44834</v>
       </c>
+      <c r="I20">
+        <v>19</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5057,6 +5494,9 @@
       <c r="H21" s="2">
         <v>44926</v>
       </c>
+      <c r="I21">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5089,6 +5529,9 @@
       <c r="H22" s="2">
         <v>43190</v>
       </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5121,6 +5564,9 @@
       <c r="H23" s="2">
         <v>43281</v>
       </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5153,6 +5599,9 @@
       <c r="H24" s="2">
         <v>43373</v>
       </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5185,6 +5634,9 @@
       <c r="H25" s="2">
         <v>43465</v>
       </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5217,6 +5669,9 @@
       <c r="H26" s="2">
         <v>43555</v>
       </c>
+      <c r="I26">
+        <v>5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5249,6 +5704,9 @@
       <c r="H27" s="2">
         <v>43646</v>
       </c>
+      <c r="I27">
+        <v>6</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5281,6 +5739,9 @@
       <c r="H28" s="2">
         <v>43738</v>
       </c>
+      <c r="I28">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5313,6 +5774,9 @@
       <c r="H29" s="2">
         <v>43830</v>
       </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5345,6 +5809,9 @@
       <c r="H30" s="2">
         <v>43921</v>
       </c>
+      <c r="I30">
+        <v>9</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5377,6 +5844,9 @@
       <c r="H31" s="2">
         <v>44012</v>
       </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5409,6 +5879,9 @@
       <c r="H32" s="2">
         <v>44104</v>
       </c>
+      <c r="I32">
+        <v>11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5441,6 +5914,9 @@
       <c r="H33" s="2">
         <v>44196</v>
       </c>
+      <c r="I33">
+        <v>12</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5473,6 +5949,9 @@
       <c r="H34" s="2">
         <v>44286</v>
       </c>
+      <c r="I34">
+        <v>13</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5505,6 +5984,9 @@
       <c r="H35" s="2">
         <v>44377</v>
       </c>
+      <c r="I35">
+        <v>14</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5537,6 +6019,9 @@
       <c r="H36" s="2">
         <v>44469</v>
       </c>
+      <c r="I36">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5569,6 +6054,9 @@
       <c r="H37" s="2">
         <v>44561</v>
       </c>
+      <c r="I37">
+        <v>16</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5601,6 +6089,9 @@
       <c r="H38" s="2">
         <v>44651</v>
       </c>
+      <c r="I38">
+        <v>17</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5633,6 +6124,9 @@
       <c r="H39" s="2">
         <v>44742</v>
       </c>
+      <c r="I39">
+        <v>18</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5665,6 +6159,9 @@
       <c r="H40" s="2">
         <v>44834</v>
       </c>
+      <c r="I40">
+        <v>19</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5696,6 +6193,9 @@
       </c>
       <c r="H41" s="2">
         <v>44926</v>
+      </c>
+      <c r="I41">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -5705,7 +6205,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -5753,6 +6253,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Running_Quarter</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5785,6 +6290,9 @@
       <c r="H2" s="2">
         <v>43190</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5817,6 +6325,9 @@
       <c r="H3" s="2">
         <v>43281</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5849,6 +6360,9 @@
       <c r="H4" s="2">
         <v>43373</v>
       </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5881,6 +6395,9 @@
       <c r="H5" s="2">
         <v>43465</v>
       </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5913,6 +6430,9 @@
       <c r="H6" s="2">
         <v>43555</v>
       </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5945,6 +6465,9 @@
       <c r="H7" s="2">
         <v>43646</v>
       </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5977,6 +6500,9 @@
       <c r="H8" s="2">
         <v>43738</v>
       </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6009,6 +6535,9 @@
       <c r="H9" s="2">
         <v>43830</v>
       </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6041,6 +6570,9 @@
       <c r="H10" s="2">
         <v>43921</v>
       </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6073,6 +6605,9 @@
       <c r="H11" s="2">
         <v>44012</v>
       </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6105,6 +6640,9 @@
       <c r="H12" s="2">
         <v>44104</v>
       </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6137,6 +6675,9 @@
       <c r="H13" s="2">
         <v>44196</v>
       </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6169,6 +6710,9 @@
       <c r="H14" s="2">
         <v>44286</v>
       </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6201,6 +6745,9 @@
       <c r="H15" s="2">
         <v>44377</v>
       </c>
+      <c r="I15">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6233,6 +6780,9 @@
       <c r="H16" s="2">
         <v>44469</v>
       </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6265,6 +6815,9 @@
       <c r="H17" s="2">
         <v>44561</v>
       </c>
+      <c r="I17">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6297,6 +6850,9 @@
       <c r="H18" s="2">
         <v>44651</v>
       </c>
+      <c r="I18">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6329,6 +6885,9 @@
       <c r="H19" s="2">
         <v>44742</v>
       </c>
+      <c r="I19">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6361,6 +6920,9 @@
       <c r="H20" s="2">
         <v>44834</v>
       </c>
+      <c r="I20">
+        <v>19</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6393,6 +6955,9 @@
       <c r="H21" s="2">
         <v>44926</v>
       </c>
+      <c r="I21">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6425,6 +6990,9 @@
       <c r="H22" s="2">
         <v>43190</v>
       </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6457,6 +7025,9 @@
       <c r="H23" s="2">
         <v>43281</v>
       </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6489,6 +7060,9 @@
       <c r="H24" s="2">
         <v>43373</v>
       </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6521,6 +7095,9 @@
       <c r="H25" s="2">
         <v>43465</v>
       </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6553,6 +7130,9 @@
       <c r="H26" s="2">
         <v>43555</v>
       </c>
+      <c r="I26">
+        <v>5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6585,6 +7165,9 @@
       <c r="H27" s="2">
         <v>43646</v>
       </c>
+      <c r="I27">
+        <v>6</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6617,6 +7200,9 @@
       <c r="H28" s="2">
         <v>43738</v>
       </c>
+      <c r="I28">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6649,6 +7235,9 @@
       <c r="H29" s="2">
         <v>43830</v>
       </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6681,6 +7270,9 @@
       <c r="H30" s="2">
         <v>43921</v>
       </c>
+      <c r="I30">
+        <v>9</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6713,6 +7305,9 @@
       <c r="H31" s="2">
         <v>44012</v>
       </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6745,6 +7340,9 @@
       <c r="H32" s="2">
         <v>44104</v>
       </c>
+      <c r="I32">
+        <v>11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6777,6 +7375,9 @@
       <c r="H33" s="2">
         <v>44196</v>
       </c>
+      <c r="I33">
+        <v>12</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6809,6 +7410,9 @@
       <c r="H34" s="2">
         <v>44286</v>
       </c>
+      <c r="I34">
+        <v>13</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6841,6 +7445,9 @@
       <c r="H35" s="2">
         <v>44377</v>
       </c>
+      <c r="I35">
+        <v>14</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6873,6 +7480,9 @@
       <c r="H36" s="2">
         <v>44469</v>
       </c>
+      <c r="I36">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6905,6 +7515,9 @@
       <c r="H37" s="2">
         <v>44561</v>
       </c>
+      <c r="I37">
+        <v>16</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6937,6 +7550,9 @@
       <c r="H38" s="2">
         <v>44651</v>
       </c>
+      <c r="I38">
+        <v>17</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6969,6 +7585,9 @@
       <c r="H39" s="2">
         <v>44742</v>
       </c>
+      <c r="I39">
+        <v>18</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7001,6 +7620,9 @@
       <c r="H40" s="2">
         <v>44834</v>
       </c>
+      <c r="I40">
+        <v>19</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7032,6 +7654,9 @@
       </c>
       <c r="H41" s="2">
         <v>44926</v>
+      </c>
+      <c r="I41">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -7041,7 +7666,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -7089,6 +7714,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Running_Quarter</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7121,6 +7751,9 @@
       <c r="H2" s="2">
         <v>43190</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7153,6 +7786,9 @@
       <c r="H3" s="2">
         <v>43281</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7185,6 +7821,9 @@
       <c r="H4" s="2">
         <v>43373</v>
       </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7217,6 +7856,9 @@
       <c r="H5" s="2">
         <v>43465</v>
       </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7249,6 +7891,9 @@
       <c r="H6" s="2">
         <v>43555</v>
       </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7281,6 +7926,9 @@
       <c r="H7" s="2">
         <v>43646</v>
       </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7313,6 +7961,9 @@
       <c r="H8" s="2">
         <v>43738</v>
       </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7345,6 +7996,9 @@
       <c r="H9" s="2">
         <v>43830</v>
       </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7377,6 +8031,9 @@
       <c r="H10" s="2">
         <v>43921</v>
       </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7409,6 +8066,9 @@
       <c r="H11" s="2">
         <v>44012</v>
       </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7441,6 +8101,9 @@
       <c r="H12" s="2">
         <v>44104</v>
       </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7473,6 +8136,9 @@
       <c r="H13" s="2">
         <v>44196</v>
       </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7505,6 +8171,9 @@
       <c r="H14" s="2">
         <v>44286</v>
       </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7537,6 +8206,9 @@
       <c r="H15" s="2">
         <v>44377</v>
       </c>
+      <c r="I15">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7569,6 +8241,9 @@
       <c r="H16" s="2">
         <v>44469</v>
       </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7601,6 +8276,9 @@
       <c r="H17" s="2">
         <v>44561</v>
       </c>
+      <c r="I17">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7633,6 +8311,9 @@
       <c r="H18" s="2">
         <v>44651</v>
       </c>
+      <c r="I18">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7665,6 +8346,9 @@
       <c r="H19" s="2">
         <v>44742</v>
       </c>
+      <c r="I19">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7697,6 +8381,9 @@
       <c r="H20" s="2">
         <v>44834</v>
       </c>
+      <c r="I20">
+        <v>19</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7729,6 +8416,9 @@
       <c r="H21" s="2">
         <v>44926</v>
       </c>
+      <c r="I21">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7761,6 +8451,9 @@
       <c r="H22" s="2">
         <v>43190</v>
       </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7793,6 +8486,9 @@
       <c r="H23" s="2">
         <v>43281</v>
       </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7825,6 +8521,9 @@
       <c r="H24" s="2">
         <v>43373</v>
       </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7857,6 +8556,9 @@
       <c r="H25" s="2">
         <v>43465</v>
       </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7889,6 +8591,9 @@
       <c r="H26" s="2">
         <v>43555</v>
       </c>
+      <c r="I26">
+        <v>5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7921,6 +8626,9 @@
       <c r="H27" s="2">
         <v>43646</v>
       </c>
+      <c r="I27">
+        <v>6</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7953,6 +8661,9 @@
       <c r="H28" s="2">
         <v>43738</v>
       </c>
+      <c r="I28">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7985,6 +8696,9 @@
       <c r="H29" s="2">
         <v>43830</v>
       </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8017,6 +8731,9 @@
       <c r="H30" s="2">
         <v>43921</v>
       </c>
+      <c r="I30">
+        <v>9</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8049,6 +8766,9 @@
       <c r="H31" s="2">
         <v>44012</v>
       </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8081,6 +8801,9 @@
       <c r="H32" s="2">
         <v>44104</v>
       </c>
+      <c r="I32">
+        <v>11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8113,6 +8836,9 @@
       <c r="H33" s="2">
         <v>44196</v>
       </c>
+      <c r="I33">
+        <v>12</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8145,6 +8871,9 @@
       <c r="H34" s="2">
         <v>44286</v>
       </c>
+      <c r="I34">
+        <v>13</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8177,6 +8906,9 @@
       <c r="H35" s="2">
         <v>44377</v>
       </c>
+      <c r="I35">
+        <v>14</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8209,6 +8941,9 @@
       <c r="H36" s="2">
         <v>44469</v>
       </c>
+      <c r="I36">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8241,6 +8976,9 @@
       <c r="H37" s="2">
         <v>44561</v>
       </c>
+      <c r="I37">
+        <v>16</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8273,6 +9011,9 @@
       <c r="H38" s="2">
         <v>44651</v>
       </c>
+      <c r="I38">
+        <v>17</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8305,6 +9046,9 @@
       <c r="H39" s="2">
         <v>44742</v>
       </c>
+      <c r="I39">
+        <v>18</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8337,6 +9081,9 @@
       <c r="H40" s="2">
         <v>44834</v>
       </c>
+      <c r="I40">
+        <v>19</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8368,6 +9115,9 @@
       </c>
       <c r="H41" s="2">
         <v>44926</v>
+      </c>
+      <c r="I41">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -8377,7 +9127,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -8425,6 +9175,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Running_Quarter</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8457,6 +9212,9 @@
       <c r="H2" s="2">
         <v>43190</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8489,6 +9247,9 @@
       <c r="H3" s="2">
         <v>43281</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8521,6 +9282,9 @@
       <c r="H4" s="2">
         <v>43373</v>
       </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8553,6 +9317,9 @@
       <c r="H5" s="2">
         <v>43465</v>
       </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8585,6 +9352,9 @@
       <c r="H6" s="2">
         <v>43555</v>
       </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8617,6 +9387,9 @@
       <c r="H7" s="2">
         <v>43646</v>
       </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8649,6 +9422,9 @@
       <c r="H8" s="2">
         <v>43738</v>
       </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8681,6 +9457,9 @@
       <c r="H9" s="2">
         <v>43830</v>
       </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8713,6 +9492,9 @@
       <c r="H10" s="2">
         <v>43921</v>
       </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8745,6 +9527,9 @@
       <c r="H11" s="2">
         <v>44012</v>
       </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8777,6 +9562,9 @@
       <c r="H12" s="2">
         <v>44104</v>
       </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8809,6 +9597,9 @@
       <c r="H13" s="2">
         <v>44196</v>
       </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8841,6 +9632,9 @@
       <c r="H14" s="2">
         <v>44286</v>
       </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8873,6 +9667,9 @@
       <c r="H15" s="2">
         <v>44377</v>
       </c>
+      <c r="I15">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8905,6 +9702,9 @@
       <c r="H16" s="2">
         <v>44469</v>
       </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8937,6 +9737,9 @@
       <c r="H17" s="2">
         <v>44561</v>
       </c>
+      <c r="I17">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8969,6 +9772,9 @@
       <c r="H18" s="2">
         <v>44651</v>
       </c>
+      <c r="I18">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9001,6 +9807,9 @@
       <c r="H19" s="2">
         <v>44742</v>
       </c>
+      <c r="I19">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9033,6 +9842,9 @@
       <c r="H20" s="2">
         <v>44834</v>
       </c>
+      <c r="I20">
+        <v>19</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9065,6 +9877,9 @@
       <c r="H21" s="2">
         <v>44926</v>
       </c>
+      <c r="I21">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9097,6 +9912,9 @@
       <c r="H22" s="2">
         <v>43190</v>
       </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9129,6 +9947,9 @@
       <c r="H23" s="2">
         <v>43281</v>
       </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9161,6 +9982,9 @@
       <c r="H24" s="2">
         <v>43373</v>
       </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9193,6 +10017,9 @@
       <c r="H25" s="2">
         <v>43465</v>
       </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9225,6 +10052,9 @@
       <c r="H26" s="2">
         <v>43555</v>
       </c>
+      <c r="I26">
+        <v>5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9257,6 +10087,9 @@
       <c r="H27" s="2">
         <v>43646</v>
       </c>
+      <c r="I27">
+        <v>6</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9289,6 +10122,9 @@
       <c r="H28" s="2">
         <v>43738</v>
       </c>
+      <c r="I28">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9321,6 +10157,9 @@
       <c r="H29" s="2">
         <v>43830</v>
       </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9353,6 +10192,9 @@
       <c r="H30" s="2">
         <v>43921</v>
       </c>
+      <c r="I30">
+        <v>9</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9385,6 +10227,9 @@
       <c r="H31" s="2">
         <v>44012</v>
       </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9417,6 +10262,9 @@
       <c r="H32" s="2">
         <v>44104</v>
       </c>
+      <c r="I32">
+        <v>11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9449,6 +10297,9 @@
       <c r="H33" s="2">
         <v>44196</v>
       </c>
+      <c r="I33">
+        <v>12</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9481,6 +10332,9 @@
       <c r="H34" s="2">
         <v>44286</v>
       </c>
+      <c r="I34">
+        <v>13</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9513,6 +10367,9 @@
       <c r="H35" s="2">
         <v>44377</v>
       </c>
+      <c r="I35">
+        <v>14</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9545,6 +10402,9 @@
       <c r="H36" s="2">
         <v>44469</v>
       </c>
+      <c r="I36">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9577,6 +10437,9 @@
       <c r="H37" s="2">
         <v>44561</v>
       </c>
+      <c r="I37">
+        <v>16</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9609,6 +10472,9 @@
       <c r="H38" s="2">
         <v>44651</v>
       </c>
+      <c r="I38">
+        <v>17</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9641,6 +10507,9 @@
       <c r="H39" s="2">
         <v>44742</v>
       </c>
+      <c r="I39">
+        <v>18</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9673,6 +10542,9 @@
       <c r="H40" s="2">
         <v>44834</v>
       </c>
+      <c r="I40">
+        <v>19</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9704,6 +10576,9 @@
       </c>
       <c r="H41" s="2">
         <v>44926</v>
+      </c>
+      <c r="I41">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Final Data/No Controls/State/STATE_NO_CONTROLS_VIC_QLD_New_Bonds.xlsx
+++ b/Data/Final Data/No Controls/State/STATE_NO_CONTROLS_VIC_QLD_New_Bonds.xlsx
@@ -361,7 +361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="20.7109375" style="2" customWidth="1"/>
@@ -414,6 +414,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Treated_Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -449,6 +454,9 @@
       <c r="I2" s="2">
         <v>43190</v>
       </c>
+      <c r="J2">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -484,6 +492,9 @@
       <c r="I3" s="2">
         <v>43281</v>
       </c>
+      <c r="J3">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -519,6 +530,9 @@
       <c r="I4" s="2">
         <v>43373</v>
       </c>
+      <c r="J4">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -554,6 +568,9 @@
       <c r="I5" s="2">
         <v>43465</v>
       </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -589,6 +606,9 @@
       <c r="I6" s="2">
         <v>43555</v>
       </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -624,6 +644,9 @@
       <c r="I7" s="2">
         <v>43646</v>
       </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -659,6 +682,9 @@
       <c r="I8" s="2">
         <v>43738</v>
       </c>
+      <c r="J8">
+        <v>13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -694,6 +720,9 @@
       <c r="I9" s="2">
         <v>43830</v>
       </c>
+      <c r="J9">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -729,6 +758,9 @@
       <c r="I10" s="2">
         <v>43921</v>
       </c>
+      <c r="J10">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -764,6 +796,9 @@
       <c r="I11" s="2">
         <v>44012</v>
       </c>
+      <c r="J11">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,6 +834,9 @@
       <c r="I12" s="2">
         <v>44104</v>
       </c>
+      <c r="J12">
+        <v>13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -834,6 +872,9 @@
       <c r="I13" s="2">
         <v>44196</v>
       </c>
+      <c r="J13">
+        <v>13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -869,6 +910,9 @@
       <c r="I14" s="2">
         <v>44286</v>
       </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -904,6 +948,9 @@
       <c r="I15" s="2">
         <v>44377</v>
       </c>
+      <c r="J15">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -939,6 +986,9 @@
       <c r="I16" s="2">
         <v>44469</v>
       </c>
+      <c r="J16">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -974,6 +1024,9 @@
       <c r="I17" s="2">
         <v>44561</v>
       </c>
+      <c r="J17">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1009,6 +1062,9 @@
       <c r="I18" s="2">
         <v>44651</v>
       </c>
+      <c r="J18">
+        <v>13</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1044,6 +1100,9 @@
       <c r="I19" s="2">
         <v>44742</v>
       </c>
+      <c r="J19">
+        <v>13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1079,6 +1138,9 @@
       <c r="I20" s="2">
         <v>44834</v>
       </c>
+      <c r="J20">
+        <v>13</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1114,6 +1176,9 @@
       <c r="I21" s="2">
         <v>44926</v>
       </c>
+      <c r="J21">
+        <v>13</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1149,6 +1214,9 @@
       <c r="I22" s="2">
         <v>45016</v>
       </c>
+      <c r="J22">
+        <v>13</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1184,6 +1252,9 @@
       <c r="I23" s="2">
         <v>45107</v>
       </c>
+      <c r="J23">
+        <v>13</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1219,6 +1290,9 @@
       <c r="I24" s="2">
         <v>45199</v>
       </c>
+      <c r="J24">
+        <v>13</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1254,6 +1328,9 @@
       <c r="I25" s="2">
         <v>45291</v>
       </c>
+      <c r="J25">
+        <v>13</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1289,6 +1366,9 @@
       <c r="I26" s="2">
         <v>45382</v>
       </c>
+      <c r="J26">
+        <v>13</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1324,6 +1404,9 @@
       <c r="I27" s="2">
         <v>43190</v>
       </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1359,6 +1442,9 @@
       <c r="I28" s="2">
         <v>43281</v>
       </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1394,6 +1480,9 @@
       <c r="I29" s="2">
         <v>43373</v>
       </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1429,6 +1518,9 @@
       <c r="I30" s="2">
         <v>43465</v>
       </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1464,6 +1556,9 @@
       <c r="I31" s="2">
         <v>43555</v>
       </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1499,6 +1594,9 @@
       <c r="I32" s="2">
         <v>43646</v>
       </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1534,6 +1632,9 @@
       <c r="I33" s="2">
         <v>43738</v>
       </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1569,6 +1670,9 @@
       <c r="I34" s="2">
         <v>43830</v>
       </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1604,6 +1708,9 @@
       <c r="I35" s="2">
         <v>43921</v>
       </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1639,6 +1746,9 @@
       <c r="I36" s="2">
         <v>44012</v>
       </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1674,6 +1784,9 @@
       <c r="I37" s="2">
         <v>44104</v>
       </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1709,6 +1822,9 @@
       <c r="I38" s="2">
         <v>44196</v>
       </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1744,6 +1860,9 @@
       <c r="I39" s="2">
         <v>44286</v>
       </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1779,6 +1898,9 @@
       <c r="I40" s="2">
         <v>44377</v>
       </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1814,6 +1936,9 @@
       <c r="I41" s="2">
         <v>44469</v>
       </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1849,6 +1974,9 @@
       <c r="I42" s="2">
         <v>44561</v>
       </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1884,6 +2012,9 @@
       <c r="I43" s="2">
         <v>44651</v>
       </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1919,6 +2050,9 @@
       <c r="I44" s="2">
         <v>44742</v>
       </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1954,6 +2088,9 @@
       <c r="I45" s="2">
         <v>44834</v>
       </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1989,6 +2126,9 @@
       <c r="I46" s="2">
         <v>44926</v>
       </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2024,6 +2164,9 @@
       <c r="I47" s="2">
         <v>45016</v>
       </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2059,6 +2202,9 @@
       <c r="I48" s="2">
         <v>45107</v>
       </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2094,6 +2240,9 @@
       <c r="I49" s="2">
         <v>45199</v>
       </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2129,6 +2278,9 @@
       <c r="I50" s="2">
         <v>45291</v>
       </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2163,6 +2315,9 @@
       </c>
       <c r="I51" s="2">
         <v>45382</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2172,7 +2327,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="20.7109375" style="2" customWidth="1"/>
@@ -2225,6 +2380,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Treated_Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2260,6 +2420,9 @@
       <c r="I2" s="2">
         <v>43190</v>
       </c>
+      <c r="J2">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2295,6 +2458,9 @@
       <c r="I3" s="2">
         <v>43281</v>
       </c>
+      <c r="J3">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2330,6 +2496,9 @@
       <c r="I4" s="2">
         <v>43373</v>
       </c>
+      <c r="J4">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2365,6 +2534,9 @@
       <c r="I5" s="2">
         <v>43465</v>
       </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2400,6 +2572,9 @@
       <c r="I6" s="2">
         <v>43555</v>
       </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2435,6 +2610,9 @@
       <c r="I7" s="2">
         <v>43646</v>
       </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2470,6 +2648,9 @@
       <c r="I8" s="2">
         <v>43738</v>
       </c>
+      <c r="J8">
+        <v>13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2505,6 +2686,9 @@
       <c r="I9" s="2">
         <v>43830</v>
       </c>
+      <c r="J9">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2540,6 +2724,9 @@
       <c r="I10" s="2">
         <v>43921</v>
       </c>
+      <c r="J10">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2575,6 +2762,9 @@
       <c r="I11" s="2">
         <v>44012</v>
       </c>
+      <c r="J11">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2610,6 +2800,9 @@
       <c r="I12" s="2">
         <v>44104</v>
       </c>
+      <c r="J12">
+        <v>13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2645,6 +2838,9 @@
       <c r="I13" s="2">
         <v>44196</v>
       </c>
+      <c r="J13">
+        <v>13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2680,6 +2876,9 @@
       <c r="I14" s="2">
         <v>44286</v>
       </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2715,6 +2914,9 @@
       <c r="I15" s="2">
         <v>44377</v>
       </c>
+      <c r="J15">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2750,6 +2952,9 @@
       <c r="I16" s="2">
         <v>44469</v>
       </c>
+      <c r="J16">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2785,6 +2990,9 @@
       <c r="I17" s="2">
         <v>44561</v>
       </c>
+      <c r="J17">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2820,6 +3028,9 @@
       <c r="I18" s="2">
         <v>44651</v>
       </c>
+      <c r="J18">
+        <v>13</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2855,6 +3066,9 @@
       <c r="I19" s="2">
         <v>44742</v>
       </c>
+      <c r="J19">
+        <v>13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2890,6 +3104,9 @@
       <c r="I20" s="2">
         <v>44834</v>
       </c>
+      <c r="J20">
+        <v>13</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2925,6 +3142,9 @@
       <c r="I21" s="2">
         <v>44926</v>
       </c>
+      <c r="J21">
+        <v>13</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2960,6 +3180,9 @@
       <c r="I22" s="2">
         <v>45016</v>
       </c>
+      <c r="J22">
+        <v>13</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2995,6 +3218,9 @@
       <c r="I23" s="2">
         <v>45107</v>
       </c>
+      <c r="J23">
+        <v>13</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3030,6 +3256,9 @@
       <c r="I24" s="2">
         <v>45199</v>
       </c>
+      <c r="J24">
+        <v>13</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3065,6 +3294,9 @@
       <c r="I25" s="2">
         <v>45291</v>
       </c>
+      <c r="J25">
+        <v>13</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3100,6 +3332,9 @@
       <c r="I26" s="2">
         <v>45382</v>
       </c>
+      <c r="J26">
+        <v>13</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3135,6 +3370,9 @@
       <c r="I27" s="2">
         <v>43190</v>
       </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3170,6 +3408,9 @@
       <c r="I28" s="2">
         <v>43281</v>
       </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3205,6 +3446,9 @@
       <c r="I29" s="2">
         <v>43373</v>
       </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3240,6 +3484,9 @@
       <c r="I30" s="2">
         <v>43465</v>
       </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3275,6 +3522,9 @@
       <c r="I31" s="2">
         <v>43555</v>
       </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3310,6 +3560,9 @@
       <c r="I32" s="2">
         <v>43646</v>
       </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3345,6 +3598,9 @@
       <c r="I33" s="2">
         <v>43738</v>
       </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3380,6 +3636,9 @@
       <c r="I34" s="2">
         <v>43830</v>
       </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3415,6 +3674,9 @@
       <c r="I35" s="2">
         <v>43921</v>
       </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3450,6 +3712,9 @@
       <c r="I36" s="2">
         <v>44012</v>
       </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3485,6 +3750,9 @@
       <c r="I37" s="2">
         <v>44104</v>
       </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3520,6 +3788,9 @@
       <c r="I38" s="2">
         <v>44196</v>
       </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3555,6 +3826,9 @@
       <c r="I39" s="2">
         <v>44286</v>
       </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3590,6 +3864,9 @@
       <c r="I40" s="2">
         <v>44377</v>
       </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3625,6 +3902,9 @@
       <c r="I41" s="2">
         <v>44469</v>
       </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3660,6 +3940,9 @@
       <c r="I42" s="2">
         <v>44561</v>
       </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3695,6 +3978,9 @@
       <c r="I43" s="2">
         <v>44651</v>
       </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3730,6 +4016,9 @@
       <c r="I44" s="2">
         <v>44742</v>
       </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3765,6 +4054,9 @@
       <c r="I45" s="2">
         <v>44834</v>
       </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3800,6 +4092,9 @@
       <c r="I46" s="2">
         <v>44926</v>
       </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3835,6 +4130,9 @@
       <c r="I47" s="2">
         <v>45016</v>
       </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3870,6 +4168,9 @@
       <c r="I48" s="2">
         <v>45107</v>
       </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3905,6 +4206,9 @@
       <c r="I49" s="2">
         <v>45199</v>
       </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3940,6 +4244,9 @@
       <c r="I50" s="2">
         <v>45291</v>
       </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3974,6 +4281,9 @@
       </c>
       <c r="I51" s="2">
         <v>45382</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3983,7 +4293,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="20.7109375" style="2" customWidth="1"/>
@@ -4036,6 +4346,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Treated_Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4071,6 +4386,9 @@
       <c r="I2" s="2">
         <v>43190</v>
       </c>
+      <c r="J2">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4106,6 +4424,9 @@
       <c r="I3" s="2">
         <v>43281</v>
       </c>
+      <c r="J3">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4141,6 +4462,9 @@
       <c r="I4" s="2">
         <v>43373</v>
       </c>
+      <c r="J4">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4176,6 +4500,9 @@
       <c r="I5" s="2">
         <v>43465</v>
       </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4211,6 +4538,9 @@
       <c r="I6" s="2">
         <v>43555</v>
       </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4246,6 +4576,9 @@
       <c r="I7" s="2">
         <v>43646</v>
       </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4281,6 +4614,9 @@
       <c r="I8" s="2">
         <v>43738</v>
       </c>
+      <c r="J8">
+        <v>13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4316,6 +4652,9 @@
       <c r="I9" s="2">
         <v>43830</v>
       </c>
+      <c r="J9">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4351,6 +4690,9 @@
       <c r="I10" s="2">
         <v>43921</v>
       </c>
+      <c r="J10">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4386,6 +4728,9 @@
       <c r="I11" s="2">
         <v>44012</v>
       </c>
+      <c r="J11">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4421,6 +4766,9 @@
       <c r="I12" s="2">
         <v>44104</v>
       </c>
+      <c r="J12">
+        <v>13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4456,6 +4804,9 @@
       <c r="I13" s="2">
         <v>44196</v>
       </c>
+      <c r="J13">
+        <v>13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4491,6 +4842,9 @@
       <c r="I14" s="2">
         <v>44286</v>
       </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4526,6 +4880,9 @@
       <c r="I15" s="2">
         <v>44377</v>
       </c>
+      <c r="J15">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4561,6 +4918,9 @@
       <c r="I16" s="2">
         <v>44469</v>
       </c>
+      <c r="J16">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4596,6 +4956,9 @@
       <c r="I17" s="2">
         <v>44561</v>
       </c>
+      <c r="J17">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4631,6 +4994,9 @@
       <c r="I18" s="2">
         <v>44651</v>
       </c>
+      <c r="J18">
+        <v>13</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4666,6 +5032,9 @@
       <c r="I19" s="2">
         <v>44742</v>
       </c>
+      <c r="J19">
+        <v>13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4701,6 +5070,9 @@
       <c r="I20" s="2">
         <v>44834</v>
       </c>
+      <c r="J20">
+        <v>13</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4736,6 +5108,9 @@
       <c r="I21" s="2">
         <v>44926</v>
       </c>
+      <c r="J21">
+        <v>13</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4771,6 +5146,9 @@
       <c r="I22" s="2">
         <v>45016</v>
       </c>
+      <c r="J22">
+        <v>13</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4806,6 +5184,9 @@
       <c r="I23" s="2">
         <v>45107</v>
       </c>
+      <c r="J23">
+        <v>13</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4841,6 +5222,9 @@
       <c r="I24" s="2">
         <v>45199</v>
       </c>
+      <c r="J24">
+        <v>13</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4876,6 +5260,9 @@
       <c r="I25" s="2">
         <v>45291</v>
       </c>
+      <c r="J25">
+        <v>13</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4911,6 +5298,9 @@
       <c r="I26" s="2">
         <v>45382</v>
       </c>
+      <c r="J26">
+        <v>13</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4946,6 +5336,9 @@
       <c r="I27" s="2">
         <v>43190</v>
       </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4981,6 +5374,9 @@
       <c r="I28" s="2">
         <v>43281</v>
       </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5016,6 +5412,9 @@
       <c r="I29" s="2">
         <v>43373</v>
       </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5051,6 +5450,9 @@
       <c r="I30" s="2">
         <v>43465</v>
       </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5086,6 +5488,9 @@
       <c r="I31" s="2">
         <v>43555</v>
       </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5121,6 +5526,9 @@
       <c r="I32" s="2">
         <v>43646</v>
       </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5156,6 +5564,9 @@
       <c r="I33" s="2">
         <v>43738</v>
       </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5191,6 +5602,9 @@
       <c r="I34" s="2">
         <v>43830</v>
       </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5226,6 +5640,9 @@
       <c r="I35" s="2">
         <v>43921</v>
       </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5261,6 +5678,9 @@
       <c r="I36" s="2">
         <v>44012</v>
       </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5296,6 +5716,9 @@
       <c r="I37" s="2">
         <v>44104</v>
       </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5331,6 +5754,9 @@
       <c r="I38" s="2">
         <v>44196</v>
       </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5366,6 +5792,9 @@
       <c r="I39" s="2">
         <v>44286</v>
       </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5401,6 +5830,9 @@
       <c r="I40" s="2">
         <v>44377</v>
       </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5436,6 +5868,9 @@
       <c r="I41" s="2">
         <v>44469</v>
       </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5471,6 +5906,9 @@
       <c r="I42" s="2">
         <v>44561</v>
       </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5506,6 +5944,9 @@
       <c r="I43" s="2">
         <v>44651</v>
       </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5541,6 +5982,9 @@
       <c r="I44" s="2">
         <v>44742</v>
       </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5576,6 +6020,9 @@
       <c r="I45" s="2">
         <v>44834</v>
       </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5611,6 +6058,9 @@
       <c r="I46" s="2">
         <v>44926</v>
       </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5646,6 +6096,9 @@
       <c r="I47" s="2">
         <v>45016</v>
       </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5681,6 +6134,9 @@
       <c r="I48" s="2">
         <v>45107</v>
       </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5716,6 +6172,9 @@
       <c r="I49" s="2">
         <v>45199</v>
       </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5751,6 +6210,9 @@
       <c r="I50" s="2">
         <v>45291</v>
       </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5785,6 +6247,9 @@
       </c>
       <c r="I51" s="2">
         <v>45382</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5794,7 +6259,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="20.7109375" style="2" customWidth="1"/>
@@ -5847,6 +6312,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Treated_Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5882,6 +6352,9 @@
       <c r="I2" s="2">
         <v>43190</v>
       </c>
+      <c r="J2">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5917,6 +6390,9 @@
       <c r="I3" s="2">
         <v>43281</v>
       </c>
+      <c r="J3">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5952,6 +6428,9 @@
       <c r="I4" s="2">
         <v>43373</v>
       </c>
+      <c r="J4">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5987,6 +6466,9 @@
       <c r="I5" s="2">
         <v>43465</v>
       </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6022,6 +6504,9 @@
       <c r="I6" s="2">
         <v>43555</v>
       </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6057,6 +6542,9 @@
       <c r="I7" s="2">
         <v>43646</v>
       </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6092,6 +6580,9 @@
       <c r="I8" s="2">
         <v>43738</v>
       </c>
+      <c r="J8">
+        <v>13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6127,6 +6618,9 @@
       <c r="I9" s="2">
         <v>43830</v>
       </c>
+      <c r="J9">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6162,6 +6656,9 @@
       <c r="I10" s="2">
         <v>43921</v>
       </c>
+      <c r="J10">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6197,6 +6694,9 @@
       <c r="I11" s="2">
         <v>44012</v>
       </c>
+      <c r="J11">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6232,6 +6732,9 @@
       <c r="I12" s="2">
         <v>44104</v>
       </c>
+      <c r="J12">
+        <v>13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6267,6 +6770,9 @@
       <c r="I13" s="2">
         <v>44196</v>
       </c>
+      <c r="J13">
+        <v>13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6302,6 +6808,9 @@
       <c r="I14" s="2">
         <v>44286</v>
       </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6337,6 +6846,9 @@
       <c r="I15" s="2">
         <v>44377</v>
       </c>
+      <c r="J15">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6372,6 +6884,9 @@
       <c r="I16" s="2">
         <v>44469</v>
       </c>
+      <c r="J16">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6407,6 +6922,9 @@
       <c r="I17" s="2">
         <v>44561</v>
       </c>
+      <c r="J17">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6442,6 +6960,9 @@
       <c r="I18" s="2">
         <v>44651</v>
       </c>
+      <c r="J18">
+        <v>13</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6477,6 +6998,9 @@
       <c r="I19" s="2">
         <v>44742</v>
       </c>
+      <c r="J19">
+        <v>13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6512,6 +7036,9 @@
       <c r="I20" s="2">
         <v>44834</v>
       </c>
+      <c r="J20">
+        <v>13</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6547,6 +7074,9 @@
       <c r="I21" s="2">
         <v>44926</v>
       </c>
+      <c r="J21">
+        <v>13</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6582,6 +7112,9 @@
       <c r="I22" s="2">
         <v>45016</v>
       </c>
+      <c r="J22">
+        <v>13</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6617,6 +7150,9 @@
       <c r="I23" s="2">
         <v>45107</v>
       </c>
+      <c r="J23">
+        <v>13</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6652,6 +7188,9 @@
       <c r="I24" s="2">
         <v>45199</v>
       </c>
+      <c r="J24">
+        <v>13</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6687,6 +7226,9 @@
       <c r="I25" s="2">
         <v>45291</v>
       </c>
+      <c r="J25">
+        <v>13</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6722,6 +7264,9 @@
       <c r="I26" s="2">
         <v>45382</v>
       </c>
+      <c r="J26">
+        <v>13</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6757,6 +7302,9 @@
       <c r="I27" s="2">
         <v>43190</v>
       </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6792,6 +7340,9 @@
       <c r="I28" s="2">
         <v>43281</v>
       </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6827,6 +7378,9 @@
       <c r="I29" s="2">
         <v>43373</v>
       </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6862,6 +7416,9 @@
       <c r="I30" s="2">
         <v>43465</v>
       </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6897,6 +7454,9 @@
       <c r="I31" s="2">
         <v>43555</v>
       </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6932,6 +7492,9 @@
       <c r="I32" s="2">
         <v>43646</v>
       </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6967,6 +7530,9 @@
       <c r="I33" s="2">
         <v>43738</v>
       </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7002,6 +7568,9 @@
       <c r="I34" s="2">
         <v>43830</v>
       </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7037,6 +7606,9 @@
       <c r="I35" s="2">
         <v>43921</v>
       </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7072,6 +7644,9 @@
       <c r="I36" s="2">
         <v>44012</v>
       </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7107,6 +7682,9 @@
       <c r="I37" s="2">
         <v>44104</v>
       </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7142,6 +7720,9 @@
       <c r="I38" s="2">
         <v>44196</v>
       </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7177,6 +7758,9 @@
       <c r="I39" s="2">
         <v>44286</v>
       </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7212,6 +7796,9 @@
       <c r="I40" s="2">
         <v>44377</v>
       </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7247,6 +7834,9 @@
       <c r="I41" s="2">
         <v>44469</v>
       </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7282,6 +7872,9 @@
       <c r="I42" s="2">
         <v>44561</v>
       </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7317,6 +7910,9 @@
       <c r="I43" s="2">
         <v>44651</v>
       </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7352,6 +7948,9 @@
       <c r="I44" s="2">
         <v>44742</v>
       </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7387,6 +7986,9 @@
       <c r="I45" s="2">
         <v>44834</v>
       </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7422,6 +8024,9 @@
       <c r="I46" s="2">
         <v>44926</v>
       </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7457,6 +8062,9 @@
       <c r="I47" s="2">
         <v>45016</v>
       </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7492,6 +8100,9 @@
       <c r="I48" s="2">
         <v>45107</v>
       </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7527,6 +8138,9 @@
       <c r="I49" s="2">
         <v>45199</v>
       </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7562,6 +8176,9 @@
       <c r="I50" s="2">
         <v>45291</v>
       </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7596,6 +8213,9 @@
       </c>
       <c r="I51" s="2">
         <v>45382</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7605,7 +8225,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="20.7109375" style="2" customWidth="1"/>
@@ -7658,6 +8278,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Treated_Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7693,6 +8318,9 @@
       <c r="I2" s="2">
         <v>43190</v>
       </c>
+      <c r="J2">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7728,6 +8356,9 @@
       <c r="I3" s="2">
         <v>43281</v>
       </c>
+      <c r="J3">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7763,6 +8394,9 @@
       <c r="I4" s="2">
         <v>43373</v>
       </c>
+      <c r="J4">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7798,6 +8432,9 @@
       <c r="I5" s="2">
         <v>43465</v>
       </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7833,6 +8470,9 @@
       <c r="I6" s="2">
         <v>43555</v>
       </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7868,6 +8508,9 @@
       <c r="I7" s="2">
         <v>43646</v>
       </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7903,6 +8546,9 @@
       <c r="I8" s="2">
         <v>43738</v>
       </c>
+      <c r="J8">
+        <v>13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7938,6 +8584,9 @@
       <c r="I9" s="2">
         <v>43830</v>
       </c>
+      <c r="J9">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7973,6 +8622,9 @@
       <c r="I10" s="2">
         <v>43921</v>
       </c>
+      <c r="J10">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8008,6 +8660,9 @@
       <c r="I11" s="2">
         <v>44012</v>
       </c>
+      <c r="J11">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8043,6 +8698,9 @@
       <c r="I12" s="2">
         <v>44104</v>
       </c>
+      <c r="J12">
+        <v>13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8078,6 +8736,9 @@
       <c r="I13" s="2">
         <v>44196</v>
       </c>
+      <c r="J13">
+        <v>13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8113,6 +8774,9 @@
       <c r="I14" s="2">
         <v>44286</v>
       </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8148,6 +8812,9 @@
       <c r="I15" s="2">
         <v>44377</v>
       </c>
+      <c r="J15">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8183,6 +8850,9 @@
       <c r="I16" s="2">
         <v>44469</v>
       </c>
+      <c r="J16">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8218,6 +8888,9 @@
       <c r="I17" s="2">
         <v>44561</v>
       </c>
+      <c r="J17">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8253,6 +8926,9 @@
       <c r="I18" s="2">
         <v>44651</v>
       </c>
+      <c r="J18">
+        <v>13</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8288,6 +8964,9 @@
       <c r="I19" s="2">
         <v>44742</v>
       </c>
+      <c r="J19">
+        <v>13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8323,6 +9002,9 @@
       <c r="I20" s="2">
         <v>44834</v>
       </c>
+      <c r="J20">
+        <v>13</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8358,6 +9040,9 @@
       <c r="I21" s="2">
         <v>44926</v>
       </c>
+      <c r="J21">
+        <v>13</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8393,6 +9078,9 @@
       <c r="I22" s="2">
         <v>45016</v>
       </c>
+      <c r="J22">
+        <v>13</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8428,6 +9116,9 @@
       <c r="I23" s="2">
         <v>45107</v>
       </c>
+      <c r="J23">
+        <v>13</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8463,6 +9154,9 @@
       <c r="I24" s="2">
         <v>45199</v>
       </c>
+      <c r="J24">
+        <v>13</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8498,6 +9192,9 @@
       <c r="I25" s="2">
         <v>45291</v>
       </c>
+      <c r="J25">
+        <v>13</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8533,6 +9230,9 @@
       <c r="I26" s="2">
         <v>45382</v>
       </c>
+      <c r="J26">
+        <v>13</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8568,6 +9268,9 @@
       <c r="I27" s="2">
         <v>43190</v>
       </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8603,6 +9306,9 @@
       <c r="I28" s="2">
         <v>43281</v>
       </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8638,6 +9344,9 @@
       <c r="I29" s="2">
         <v>43373</v>
       </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8673,6 +9382,9 @@
       <c r="I30" s="2">
         <v>43465</v>
       </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8708,6 +9420,9 @@
       <c r="I31" s="2">
         <v>43555</v>
       </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8743,6 +9458,9 @@
       <c r="I32" s="2">
         <v>43646</v>
       </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8778,6 +9496,9 @@
       <c r="I33" s="2">
         <v>43738</v>
       </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8813,6 +9534,9 @@
       <c r="I34" s="2">
         <v>43830</v>
       </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8848,6 +9572,9 @@
       <c r="I35" s="2">
         <v>43921</v>
       </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8883,6 +9610,9 @@
       <c r="I36" s="2">
         <v>44012</v>
       </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8918,6 +9648,9 @@
       <c r="I37" s="2">
         <v>44104</v>
       </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8953,6 +9686,9 @@
       <c r="I38" s="2">
         <v>44196</v>
       </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8988,6 +9724,9 @@
       <c r="I39" s="2">
         <v>44286</v>
       </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9023,6 +9762,9 @@
       <c r="I40" s="2">
         <v>44377</v>
       </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9058,6 +9800,9 @@
       <c r="I41" s="2">
         <v>44469</v>
       </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9093,6 +9838,9 @@
       <c r="I42" s="2">
         <v>44561</v>
       </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9128,6 +9876,9 @@
       <c r="I43" s="2">
         <v>44651</v>
       </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9163,6 +9914,9 @@
       <c r="I44" s="2">
         <v>44742</v>
       </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9198,6 +9952,9 @@
       <c r="I45" s="2">
         <v>44834</v>
       </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9233,6 +9990,9 @@
       <c r="I46" s="2">
         <v>44926</v>
       </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9268,6 +10028,9 @@
       <c r="I47" s="2">
         <v>45016</v>
       </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9303,6 +10066,9 @@
       <c r="I48" s="2">
         <v>45107</v>
       </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9338,6 +10104,9 @@
       <c r="I49" s="2">
         <v>45199</v>
       </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9373,6 +10142,9 @@
       <c r="I50" s="2">
         <v>45291</v>
       </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9407,6 +10179,9 @@
       </c>
       <c r="I51" s="2">
         <v>45382</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9416,7 +10191,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="20.7109375" style="2" customWidth="1"/>
@@ -9469,6 +10244,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Treated_Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9504,6 +10284,9 @@
       <c r="I2" s="2">
         <v>43190</v>
       </c>
+      <c r="J2">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9539,6 +10322,9 @@
       <c r="I3" s="2">
         <v>43281</v>
       </c>
+      <c r="J3">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9574,6 +10360,9 @@
       <c r="I4" s="2">
         <v>43373</v>
       </c>
+      <c r="J4">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9609,6 +10398,9 @@
       <c r="I5" s="2">
         <v>43465</v>
       </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9644,6 +10436,9 @@
       <c r="I6" s="2">
         <v>43555</v>
       </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9679,6 +10474,9 @@
       <c r="I7" s="2">
         <v>43646</v>
       </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9714,6 +10512,9 @@
       <c r="I8" s="2">
         <v>43738</v>
       </c>
+      <c r="J8">
+        <v>13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9749,6 +10550,9 @@
       <c r="I9" s="2">
         <v>43830</v>
       </c>
+      <c r="J9">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9784,6 +10588,9 @@
       <c r="I10" s="2">
         <v>43921</v>
       </c>
+      <c r="J10">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9819,6 +10626,9 @@
       <c r="I11" s="2">
         <v>44012</v>
       </c>
+      <c r="J11">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9854,6 +10664,9 @@
       <c r="I12" s="2">
         <v>44104</v>
       </c>
+      <c r="J12">
+        <v>13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9889,6 +10702,9 @@
       <c r="I13" s="2">
         <v>44196</v>
       </c>
+      <c r="J13">
+        <v>13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9924,6 +10740,9 @@
       <c r="I14" s="2">
         <v>44286</v>
       </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9959,6 +10778,9 @@
       <c r="I15" s="2">
         <v>44377</v>
       </c>
+      <c r="J15">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9994,6 +10816,9 @@
       <c r="I16" s="2">
         <v>44469</v>
       </c>
+      <c r="J16">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10029,6 +10854,9 @@
       <c r="I17" s="2">
         <v>44561</v>
       </c>
+      <c r="J17">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10064,6 +10892,9 @@
       <c r="I18" s="2">
         <v>44651</v>
       </c>
+      <c r="J18">
+        <v>13</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10099,6 +10930,9 @@
       <c r="I19" s="2">
         <v>44742</v>
       </c>
+      <c r="J19">
+        <v>13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10134,6 +10968,9 @@
       <c r="I20" s="2">
         <v>44834</v>
       </c>
+      <c r="J20">
+        <v>13</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10169,6 +11006,9 @@
       <c r="I21" s="2">
         <v>44926</v>
       </c>
+      <c r="J21">
+        <v>13</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10204,6 +11044,9 @@
       <c r="I22" s="2">
         <v>45016</v>
       </c>
+      <c r="J22">
+        <v>13</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10239,6 +11082,9 @@
       <c r="I23" s="2">
         <v>45107</v>
       </c>
+      <c r="J23">
+        <v>13</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10274,6 +11120,9 @@
       <c r="I24" s="2">
         <v>45199</v>
       </c>
+      <c r="J24">
+        <v>13</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10309,6 +11158,9 @@
       <c r="I25" s="2">
         <v>45291</v>
       </c>
+      <c r="J25">
+        <v>13</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10344,6 +11196,9 @@
       <c r="I26" s="2">
         <v>45382</v>
       </c>
+      <c r="J26">
+        <v>13</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10379,6 +11234,9 @@
       <c r="I27" s="2">
         <v>43190</v>
       </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10414,6 +11272,9 @@
       <c r="I28" s="2">
         <v>43281</v>
       </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10449,6 +11310,9 @@
       <c r="I29" s="2">
         <v>43373</v>
       </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10484,6 +11348,9 @@
       <c r="I30" s="2">
         <v>43465</v>
       </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10519,6 +11386,9 @@
       <c r="I31" s="2">
         <v>43555</v>
       </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10554,6 +11424,9 @@
       <c r="I32" s="2">
         <v>43646</v>
       </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10589,6 +11462,9 @@
       <c r="I33" s="2">
         <v>43738</v>
       </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10624,6 +11500,9 @@
       <c r="I34" s="2">
         <v>43830</v>
       </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10659,6 +11538,9 @@
       <c r="I35" s="2">
         <v>43921</v>
       </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -10694,6 +11576,9 @@
       <c r="I36" s="2">
         <v>44012</v>
       </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10729,6 +11614,9 @@
       <c r="I37" s="2">
         <v>44104</v>
       </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10764,6 +11652,9 @@
       <c r="I38" s="2">
         <v>44196</v>
       </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -10799,6 +11690,9 @@
       <c r="I39" s="2">
         <v>44286</v>
       </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -10834,6 +11728,9 @@
       <c r="I40" s="2">
         <v>44377</v>
       </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -10869,6 +11766,9 @@
       <c r="I41" s="2">
         <v>44469</v>
       </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -10904,6 +11804,9 @@
       <c r="I42" s="2">
         <v>44561</v>
       </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -10939,6 +11842,9 @@
       <c r="I43" s="2">
         <v>44651</v>
       </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -10974,6 +11880,9 @@
       <c r="I44" s="2">
         <v>44742</v>
       </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -11009,6 +11918,9 @@
       <c r="I45" s="2">
         <v>44834</v>
       </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -11044,6 +11956,9 @@
       <c r="I46" s="2">
         <v>44926</v>
       </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -11079,6 +11994,9 @@
       <c r="I47" s="2">
         <v>45016</v>
       </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -11114,6 +12032,9 @@
       <c r="I48" s="2">
         <v>45107</v>
       </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -11149,6 +12070,9 @@
       <c r="I49" s="2">
         <v>45199</v>
       </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -11184,6 +12108,9 @@
       <c r="I50" s="2">
         <v>45291</v>
       </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -11218,6 +12145,9 @@
       </c>
       <c r="I51" s="2">
         <v>45382</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11227,7 +12157,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="20.7109375" style="2" customWidth="1"/>
@@ -11280,6 +12210,11 @@
           <t>Quarter_End_Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Treated_Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11315,6 +12250,9 @@
       <c r="I2" s="2">
         <v>43190</v>
       </c>
+      <c r="J2">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11350,6 +12288,9 @@
       <c r="I3" s="2">
         <v>43281</v>
       </c>
+      <c r="J3">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11385,6 +12326,9 @@
       <c r="I4" s="2">
         <v>43373</v>
       </c>
+      <c r="J4">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11420,6 +12364,9 @@
       <c r="I5" s="2">
         <v>43465</v>
       </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11455,6 +12402,9 @@
       <c r="I6" s="2">
         <v>43555</v>
       </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11490,6 +12440,9 @@
       <c r="I7" s="2">
         <v>43646</v>
       </c>
+      <c r="J7">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11525,6 +12478,9 @@
       <c r="I8" s="2">
         <v>43738</v>
       </c>
+      <c r="J8">
+        <v>13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11560,6 +12516,9 @@
       <c r="I9" s="2">
         <v>43830</v>
       </c>
+      <c r="J9">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11595,6 +12554,9 @@
       <c r="I10" s="2">
         <v>43921</v>
       </c>
+      <c r="J10">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11630,6 +12592,9 @@
       <c r="I11" s="2">
         <v>44012</v>
       </c>
+      <c r="J11">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11665,6 +12630,9 @@
       <c r="I12" s="2">
         <v>44104</v>
       </c>
+      <c r="J12">
+        <v>13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11700,6 +12668,9 @@
       <c r="I13" s="2">
         <v>44196</v>
       </c>
+      <c r="J13">
+        <v>13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11735,6 +12706,9 @@
       <c r="I14" s="2">
         <v>44286</v>
       </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11770,6 +12744,9 @@
       <c r="I15" s="2">
         <v>44377</v>
       </c>
+      <c r="J15">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11805,6 +12782,9 @@
       <c r="I16" s="2">
         <v>44469</v>
       </c>
+      <c r="J16">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11840,6 +12820,9 @@
       <c r="I17" s="2">
         <v>44561</v>
       </c>
+      <c r="J17">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11875,6 +12858,9 @@
       <c r="I18" s="2">
         <v>44651</v>
       </c>
+      <c r="J18">
+        <v>13</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11910,6 +12896,9 @@
       <c r="I19" s="2">
         <v>44742</v>
       </c>
+      <c r="J19">
+        <v>13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11945,6 +12934,9 @@
       <c r="I20" s="2">
         <v>44834</v>
       </c>
+      <c r="J20">
+        <v>13</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11980,6 +12972,9 @@
       <c r="I21" s="2">
         <v>44926</v>
       </c>
+      <c r="J21">
+        <v>13</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12015,6 +13010,9 @@
       <c r="I22" s="2">
         <v>45016</v>
       </c>
+      <c r="J22">
+        <v>13</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12050,6 +13048,9 @@
       <c r="I23" s="2">
         <v>45107</v>
       </c>
+      <c r="J23">
+        <v>13</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12085,6 +13086,9 @@
       <c r="I24" s="2">
         <v>45199</v>
       </c>
+      <c r="J24">
+        <v>13</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12120,6 +13124,9 @@
       <c r="I25" s="2">
         <v>45291</v>
       </c>
+      <c r="J25">
+        <v>13</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12155,6 +13162,9 @@
       <c r="I26" s="2">
         <v>45382</v>
       </c>
+      <c r="J26">
+        <v>13</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12190,6 +13200,9 @@
       <c r="I27" s="2">
         <v>43190</v>
       </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12225,6 +13238,9 @@
       <c r="I28" s="2">
         <v>43281</v>
       </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12260,6 +13276,9 @@
       <c r="I29" s="2">
         <v>43373</v>
       </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12295,6 +13314,9 @@
       <c r="I30" s="2">
         <v>43465</v>
       </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12330,6 +13352,9 @@
       <c r="I31" s="2">
         <v>43555</v>
       </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12365,6 +13390,9 @@
       <c r="I32" s="2">
         <v>43646</v>
       </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -12400,6 +13428,9 @@
       <c r="I33" s="2">
         <v>43738</v>
       </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -12435,6 +13466,9 @@
       <c r="I34" s="2">
         <v>43830</v>
       </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12470,6 +13504,9 @@
       <c r="I35" s="2">
         <v>43921</v>
       </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12505,6 +13542,9 @@
       <c r="I36" s="2">
         <v>44012</v>
       </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12540,6 +13580,9 @@
       <c r="I37" s="2">
         <v>44104</v>
       </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12575,6 +13618,9 @@
       <c r="I38" s="2">
         <v>44196</v>
       </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12610,6 +13656,9 @@
       <c r="I39" s="2">
         <v>44286</v>
       </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12645,6 +13694,9 @@
       <c r="I40" s="2">
         <v>44377</v>
       </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12680,6 +13732,9 @@
       <c r="I41" s="2">
         <v>44469</v>
       </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12715,6 +13770,9 @@
       <c r="I42" s="2">
         <v>44561</v>
       </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12750,6 +13808,9 @@
       <c r="I43" s="2">
         <v>44651</v>
       </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12785,6 +13846,9 @@
       <c r="I44" s="2">
         <v>44742</v>
       </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12820,6 +13884,9 @@
       <c r="I45" s="2">
         <v>44834</v>
       </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12855,6 +13922,9 @@
       <c r="I46" s="2">
         <v>44926</v>
       </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12890,6 +13960,9 @@
       <c r="I47" s="2">
         <v>45016</v>
       </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12925,6 +13998,9 @@
       <c r="I48" s="2">
         <v>45107</v>
       </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12960,6 +14036,9 @@
       <c r="I49" s="2">
         <v>45199</v>
       </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12995,6 +14074,9 @@
       <c r="I50" s="2">
         <v>45291</v>
       </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -13029,6 +14111,9 @@
       </c>
       <c r="I51" s="2">
         <v>45382</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
